--- a/Configs/Luban/Data/__tables__.xlsx
+++ b/Configs/Luban/Data/__tables__.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Test\Configs\Luban\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3A7ABB-0FC0-44C9-B805-C6CF73A19780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B742745B-2666-44C6-9D5F-96D654104874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13200" yWindow="6345" windowWidth="20895" windowHeight="13755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -101,13 +106,37 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>demo.TbMonster</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>demo.Monster</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster.xlsx</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>map</t>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物表</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,6 +156,20 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -160,11 +203,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -443,8 +492,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
@@ -453,7 +502,7 @@
     <col min="6" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -488,7 +537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -520,7 +569,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -541,11 +590,37 @@
       </c>
       <c r="K3" s="1" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>